--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="复盘仪表盘" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日复盘" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="板块热点" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="核心个股" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="持仓计划" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="复盘规则" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="复盘仪表盘" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="每日复盘" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="板块热点" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="核心个股" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="持仓计划" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="复盘规则" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'每日复盘'!$A$1:$Q$202</definedName>
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1043,26 +1043,26 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.0032</v>
+        <v>-0.0018</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>-0.0043</v>
+        <v>0.0039</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.0091</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3170.01</v>
+        <v>19488.98</v>
       </c>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>震荡偏弱</t>
+          <t>震荡</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>0</v>
@@ -1075,19 +1075,19 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1-2成</t>
+          <t>2-4成</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>ST摘帽/重整、其他涨停</t>
+          <t>其他涨停</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约3170.01亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：ST摘帽/重整。</t>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约19488.98亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
         </is>
       </c>
     </row>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1043,26 +1043,26 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.0018</v>
+        <v>0.004</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.0039</v>
+        <v>0.0131</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19488.98</v>
+        <v>30917.64</v>
       </c>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>震荡</t>
+          <t>震荡偏强</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>0</v>
@@ -1071,23 +1071,23 @@
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2-4成</t>
+          <t>3-5成</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>其他涨停</t>
+          <t>新材料/化工、医药/消费、PCB</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="n"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>市场震荡，指数分化但创业板较强，两市成交额约19488.98亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约30917.64亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
         </is>
       </c>
     </row>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1092,23 +1092,59 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>33101.07</v>
+      </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、半导体设备/先进封装、其他涨停</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约33101.07亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1147,23 +1147,59 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>33101.07</v>
+      </c>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、半导体设备/先进封装、其他涨停</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约33101.07亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1202,23 +1202,59 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>37371.99</v>
+      </c>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>PCB、其他涨停</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="n"/>
-      <c r="Q7" s="3" t="n"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约37371.99亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：PCB。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1257,23 +1257,59 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>-0.0137</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>-0.0317</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>-0.0384</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>34407.64</v>
+      </c>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约34407.64亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1312,23 +1312,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>32843.28</v>
+      </c>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、复合材料、PCB</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="3" t="n"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约32843.28亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1367,23 +1367,59 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>35942.88</v>
+      </c>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、PCB、复合材料</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="3" t="n"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约35942.88亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1422,23 +1422,59 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.0344</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.0407</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>35524.1</v>
+      </c>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>面板/显示、其他涨停</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约35524.1亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：面板/显示。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1477,23 +1477,59 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>35177.54</v>
+      </c>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="3" t="n"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约35177.54亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1532,23 +1532,59 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>32737.58</v>
+      </c>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>面板/显示、其他涨停</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="3" t="n"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约32737.58亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：面板/显示。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1587,23 +1587,59 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-0.0053</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>36600.04</v>
+      </c>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr"/>
       <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约36600.04亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1642,23 +1642,59 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-0.0571</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>34505.51</v>
+      </c>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="3" t="n"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约34505.51亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1697,23 +1697,59 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>31824.54</v>
+      </c>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="n"/>
-      <c r="Q16" s="3" t="n"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约31824.54亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1752,23 +1752,59 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>30911.24</v>
+      </c>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="n"/>
-      <c r="Q17" s="3" t="n"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约30911.24亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1807,23 +1807,59 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-0.0126</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>25811.57</v>
+      </c>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="3" t="n"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约25811.57亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1862,23 +1862,59 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>25635.23</v>
+      </c>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约25635.23亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1917,23 +1917,59 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.0449</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>29137.29</v>
+      </c>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>PCB、其他涨停</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
       <c r="P20" s="3" t="n"/>
-      <c r="Q20" s="3" t="n"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约29137.29亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：PCB。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1972,23 +1972,59 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-0.0229</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>33885.5</v>
+      </c>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约33885.5亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2027,23 +2027,59 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-0.0206</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>-0.0348</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>28177.61</v>
+      </c>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="3" t="n"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="n"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约28177.61亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2082,23 +2082,59 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.0136</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>27039.68</v>
+      </c>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、PCB、其他涨停</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="n"/>
-      <c r="Q23" s="3" t="n"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约27039.68亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2137,23 +2137,59 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-0.0121</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>25711.54</v>
+      </c>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="n"/>
-      <c r="Q24" s="3" t="n"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约25711.54亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2192,23 +2192,59 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.0197</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.0295</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>24035.65</v>
+      </c>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="3" t="n"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约24035.65亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2247,23 +2247,59 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>-0.0305</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>-0.05400000000000001</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>-0.07150000000000001</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>26549.59</v>
+      </c>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr"/>
       <c r="P26" s="3" t="n"/>
-      <c r="Q26" s="3" t="n"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约26549.59亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2302,23 +2302,59 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>27021.27</v>
+      </c>
       <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="n"/>
-      <c r="Q27" s="3" t="n"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约27021.27亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2357,23 +2357,59 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>29570.93</v>
+      </c>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>半导体、面板/显示、其他涨停</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr"/>
       <c r="P28" s="3" t="n"/>
-      <c r="Q28" s="3" t="n"/>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约29570.93亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：半导体。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2412,23 +2412,59 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.0323</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>26533.45</v>
+      </c>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="n"/>
-      <c r="Q29" s="3" t="n"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约26533.45亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2467,23 +2467,59 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>21953.01</v>
+      </c>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr"/>
       <c r="P30" s="3" t="n"/>
-      <c r="Q30" s="3" t="n"/>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约21953.01亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2522,23 +2522,59 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>-0.0161</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0.0247</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0.0265</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>19311.4</v>
+      </c>
       <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>医药/消费、其他涨停</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr"/>
       <c r="P31" s="3" t="n"/>
-      <c r="Q31" s="3" t="n"/>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约19311.4亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：医药/消费。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2577,23 +2577,59 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>20766.2</v>
+      </c>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、复合材料、建材/玻璃</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="n"/>
-      <c r="Q32" s="3" t="n"/>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约20766.2亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2632,23 +2632,59 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n"/>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>-0.0452</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>-0.0735</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>20257.81</v>
+      </c>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr"/>
       <c r="P33" s="3" t="n"/>
-      <c r="Q33" s="3" t="n"/>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约20257.81亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2687,23 +2687,59 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>22965.79</v>
+      </c>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="n"/>
-      <c r="L34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr"/>
       <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="3" t="n"/>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约22965.79亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2742,23 +2742,59 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>-0.0273</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>-0.0397</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>23428.09</v>
+      </c>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="n"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr"/>
       <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="n"/>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约23428.09亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2797,23 +2797,59 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n"/>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>25419.48</v>
+      </c>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
-      <c r="J36" s="3" t="n"/>
-      <c r="K36" s="3" t="n"/>
-      <c r="L36" s="3" t="n"/>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n"/>
-      <c r="O36" s="3" t="n"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>医药/消费、新材料/化工、其他涨停</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr"/>
       <c r="P36" s="3" t="n"/>
-      <c r="Q36" s="3" t="n"/>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约25419.48亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：医药/消费。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2852,23 +2852,59 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>19973.86</v>
+      </c>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="n"/>
-      <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3" t="n"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="n"/>
-      <c r="Q37" s="3" t="n"/>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约19973.86亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2907,23 +2907,59 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0.0325</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>22135.92</v>
+      </c>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n"/>
-      <c r="O38" s="3" t="n"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>PCB、新材料/化工、消费电子</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr"/>
       <c r="P38" s="3" t="n"/>
-      <c r="Q38" s="3" t="n"/>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约22135.92亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：PCB。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2962,23 +2962,59 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>26596.35</v>
+      </c>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>半导体、新材料/化工、PCB</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="n"/>
-      <c r="Q39" s="3" t="n"/>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约26596.35亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：半导体。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3017,23 +3017,59 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n"/>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0.005699999999999999</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>25287.81</v>
+      </c>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>半导体、其他涨停</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr"/>
       <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n"/>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约25287.81亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：半导体。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3072,23 +3072,59 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>25231.03</v>
+      </c>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>医药/消费、其他涨停</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="n"/>
-      <c r="Q41" s="3" t="n"/>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约25231.03亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：医药/消费。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3127,23 +3127,59 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>23209.86</v>
+      </c>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-      <c r="K42" s="3" t="n"/>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="n"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr"/>
       <c r="P42" s="3" t="n"/>
-      <c r="Q42" s="3" t="n"/>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约23209.86亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3182,23 +3182,59 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>21524.23</v>
+      </c>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>CPO/光通信、其他涨停</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="n"/>
-      <c r="Q43" s="3" t="n"/>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约21524.23亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：CPO/光通信。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3237,23 +3237,59 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>-0.004500000000000001</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>25509.17</v>
+      </c>
       <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="n"/>
-      <c r="Q44" s="3" t="n"/>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约25509.17亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3292,23 +3292,59 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>21428.43</v>
+      </c>
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、其他涨停</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="n"/>
-      <c r="Q45" s="3" t="n"/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约21428.43亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3347,23 +3347,59 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n"/>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0.0141</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>23874.57</v>
+      </c>
       <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n"/>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>PCB、其他涨停</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="n"/>
-      <c r="Q46" s="3" t="n"/>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约23874.57亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：PCB。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3402,23 +3402,59 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>24007.75</v>
+      </c>
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="n"/>
-      <c r="L47" s="3" t="n"/>
-      <c r="M47" s="3" t="n"/>
-      <c r="N47" s="3" t="n"/>
-      <c r="O47" s="3" t="n"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr"/>
       <c r="P47" s="3" t="n"/>
-      <c r="Q47" s="3" t="n"/>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约24007.75亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3457,23 +3457,59 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>-0.0501</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>-0.0626</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>25110.43</v>
+      </c>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
-      <c r="L48" s="3" t="n"/>
-      <c r="M48" s="3" t="n"/>
-      <c r="N48" s="3" t="n"/>
-      <c r="O48" s="3" t="n"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr"/>
       <c r="P48" s="3" t="n"/>
-      <c r="Q48" s="3" t="n"/>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约25110.43亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3512,23 +3512,59 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>20793.63</v>
+      </c>
       <c r="F49" s="3" t="n"/>
       <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="n"/>
-      <c r="L49" s="3" t="n"/>
-      <c r="M49" s="3" t="n"/>
-      <c r="N49" s="3" t="n"/>
-      <c r="O49" s="3" t="n"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr"/>
       <c r="P49" s="3" t="n"/>
-      <c r="Q49" s="3" t="n"/>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约20793.63亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3567,23 +3567,59 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>18792.64</v>
+      </c>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="n"/>
-      <c r="L50" s="3" t="n"/>
-      <c r="M50" s="3" t="n"/>
-      <c r="N50" s="3" t="n"/>
-      <c r="O50" s="3" t="n"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr"/>
       <c r="P50" s="3" t="n"/>
-      <c r="Q50" s="3" t="n"/>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约18792.64亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3622,23 +3622,59 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>-0.0321</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>20074.56</v>
+      </c>
       <c r="F51" s="3" t="n"/>
       <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
-      <c r="K51" s="3" t="n"/>
-      <c r="L51" s="3" t="n"/>
-      <c r="M51" s="3" t="n"/>
-      <c r="N51" s="3" t="n"/>
-      <c r="O51" s="3" t="n"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr"/>
       <c r="P51" s="3" t="n"/>
-      <c r="Q51" s="3" t="n"/>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约20074.56亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3677,23 +3677,59 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n"/>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="n"/>
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>18318.44</v>
+      </c>
       <c r="F52" s="3" t="n"/>
       <c r="G52" s="3" t="n"/>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="n"/>
-      <c r="L52" s="3" t="n"/>
-      <c r="M52" s="3" t="n"/>
-      <c r="N52" s="3" t="n"/>
-      <c r="O52" s="3" t="n"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr"/>
       <c r="P52" s="3" t="n"/>
-      <c r="Q52" s="3" t="n"/>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约18318.44亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3732,23 +3732,59 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>21259.27</v>
+      </c>
       <c r="F53" s="3" t="n"/>
       <c r="G53" s="3" t="n"/>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="n"/>
-      <c r="L53" s="3" t="n"/>
-      <c r="M53" s="3" t="n"/>
-      <c r="N53" s="3" t="n"/>
-      <c r="O53" s="3" t="n"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr"/>
       <c r="P53" s="3" t="n"/>
-      <c r="Q53" s="3" t="n"/>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约21259.27亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3787,23 +3787,59 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>21017.15</v>
+      </c>
       <c r="F54" s="3" t="n"/>
       <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="n"/>
-      <c r="L54" s="3" t="n"/>
-      <c r="M54" s="3" t="n"/>
-      <c r="N54" s="3" t="n"/>
-      <c r="O54" s="3" t="n"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr"/>
       <c r="P54" s="3" t="n"/>
-      <c r="Q54" s="3" t="n"/>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约21017.15亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3842,23 +3842,59 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n"/>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>21310.3</v>
+      </c>
       <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="n"/>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="n"/>
-      <c r="L55" s="3" t="n"/>
-      <c r="M55" s="3" t="n"/>
-      <c r="N55" s="3" t="n"/>
-      <c r="O55" s="3" t="n"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、其他涨停</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr"/>
       <c r="P55" s="3" t="n"/>
-      <c r="Q55" s="3" t="n"/>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约21310.3亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3897,23 +3897,59 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>20334.03</v>
+      </c>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="n"/>
-      <c r="L56" s="3" t="n"/>
-      <c r="M56" s="3" t="n"/>
-      <c r="N56" s="3" t="n"/>
-      <c r="O56" s="3" t="n"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr"/>
       <c r="P56" s="3" t="n"/>
-      <c r="Q56" s="3" t="n"/>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约20334.03亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3952,23 +3952,59 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n"/>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>-0.0188</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>17911.78</v>
+      </c>
       <c r="F57" s="3" t="n"/>
       <c r="G57" s="3" t="n"/>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="n"/>
-      <c r="L57" s="3" t="n"/>
-      <c r="M57" s="3" t="n"/>
-      <c r="N57" s="3" t="n"/>
-      <c r="O57" s="3" t="n"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr"/>
       <c r="P57" s="3" t="n"/>
-      <c r="Q57" s="3" t="n"/>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约17911.78亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4007,23 +4007,59 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>17589.16</v>
+      </c>
       <c r="F58" s="3" t="n"/>
       <c r="G58" s="3" t="n"/>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
-      <c r="J58" s="3" t="n"/>
-      <c r="K58" s="3" t="n"/>
-      <c r="L58" s="3" t="n"/>
-      <c r="M58" s="3" t="n"/>
-      <c r="N58" s="3" t="n"/>
-      <c r="O58" s="3" t="n"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr"/>
       <c r="P58" s="3" t="n"/>
-      <c r="Q58" s="3" t="n"/>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约17589.16亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4062,23 +4062,59 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n"/>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>20306.68</v>
+      </c>
       <c r="F59" s="3" t="n"/>
       <c r="G59" s="3" t="n"/>
-      <c r="H59" s="3" t="n"/>
-      <c r="I59" s="3" t="n"/>
-      <c r="J59" s="3" t="n"/>
-      <c r="K59" s="3" t="n"/>
-      <c r="L59" s="3" t="n"/>
-      <c r="M59" s="3" t="n"/>
-      <c r="N59" s="3" t="n"/>
-      <c r="O59" s="3" t="n"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr"/>
       <c r="P59" s="3" t="n"/>
-      <c r="Q59" s="3" t="n"/>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约20306.68亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4117,23 +4117,59 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.0341</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>19460.19</v>
+      </c>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="n"/>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
-      <c r="J60" s="3" t="n"/>
-      <c r="K60" s="3" t="n"/>
-      <c r="L60" s="3" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="N60" s="3" t="n"/>
-      <c r="O60" s="3" t="n"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>PCB、其他涨停</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr"/>
       <c r="P60" s="3" t="n"/>
-      <c r="Q60" s="3" t="n"/>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约19460.19亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：PCB。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4172,23 +4172,59 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>19603.35</v>
+      </c>
       <c r="F61" s="3" t="n"/>
       <c r="G61" s="3" t="n"/>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
-      <c r="J61" s="3" t="n"/>
-      <c r="K61" s="3" t="n"/>
-      <c r="L61" s="3" t="n"/>
-      <c r="M61" s="3" t="n"/>
-      <c r="N61" s="3" t="n"/>
-      <c r="O61" s="3" t="n"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr"/>
       <c r="P61" s="3" t="n"/>
-      <c r="Q61" s="3" t="n"/>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约19603.35亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4227,23 +4227,59 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n"/>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>18556.07</v>
+      </c>
       <c r="F62" s="3" t="n"/>
       <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="n"/>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="3" t="n"/>
-      <c r="L62" s="3" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="N62" s="3" t="n"/>
-      <c r="O62" s="3" t="n"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr"/>
       <c r="P62" s="3" t="n"/>
-      <c r="Q62" s="3" t="n"/>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约18556.07亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4282,23 +4282,59 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>16471.48</v>
+      </c>
       <c r="F63" s="3" t="n"/>
       <c r="G63" s="3" t="n"/>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="n"/>
-      <c r="L63" s="3" t="n"/>
-      <c r="M63" s="3" t="n"/>
-      <c r="N63" s="3" t="n"/>
-      <c r="O63" s="3" t="n"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、其他涨停</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr"/>
       <c r="P63" s="3" t="n"/>
-      <c r="Q63" s="3" t="n"/>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约16471.48亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4337,23 +4337,59 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n"/>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>-0.0108</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>19718.98</v>
+      </c>
       <c r="F64" s="3" t="n"/>
       <c r="G64" s="3" t="n"/>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="3" t="n"/>
-      <c r="J64" s="3" t="n"/>
-      <c r="K64" s="3" t="n"/>
-      <c r="L64" s="3" t="n"/>
-      <c r="M64" s="3" t="n"/>
-      <c r="N64" s="3" t="n"/>
-      <c r="O64" s="3" t="n"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>新材料/化工、PCB、其他涨停</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr"/>
       <c r="P64" s="3" t="n"/>
-      <c r="Q64" s="3" t="n"/>
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约19718.98亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：新材料/化工。</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
